--- a/AAII_Financials/Yearly/FLNT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FLNT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>FLNT</t>
   </si>
@@ -1011,7 +1011,7 @@
         <v>7300</v>
       </c>
       <c r="E14" s="3">
-        <v>8900</v>
+        <v>7200</v>
       </c>
       <c r="F14" s="3">
         <v>52300</v>
@@ -1250,11 +1250,11 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1700</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-7000</v>
+        <v>-7100</v>
       </c>
       <c r="E21" s="3">
-        <v>-7500</v>
+        <v>-9200</v>
       </c>
       <c r="F21" s="3">
         <v>3100</v>
@@ -1862,11 +1862,11 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-1700</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
